--- a/docs/checklist/2회차_셀프·상호_체크리스트_셀프점검.xlsx
+++ b/docs/checklist/2회차_셀프·상호_체크리스트_셀프점검.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>2026-10-23 15:50~16:25 KST</t>
+          <t>2026-10-23 16:00~16:32 KST</t>
         </is>
       </c>
       <c r="D6" s="34" t="n"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I12" s="33" t="inlineStr">
         <is>
-          <t>같은 질문 두 번: 1회차 cache_hit=false 23.3초, 2회차 cache_hit=true 13.8초, 문서 청크 수 6 유지. 2회차는 프롬프트 1·2와 수집을 건너뛰고 답변 생성만 다시 한다(테스트로 프롬프트 재호출 0회 확인).</t>
+          <t>같은 질문 두 번: 1회차 cache_hit=false 23.3초, 2회차 cache_hit=true 13.8초. 2회차는 프롬프트 1·2와 수집을 건너뛰고 답변 생성만 다시 한다(테스트로 프롬프트 재호출 0회 확인). 2회차 뒤 문서 청크 6개(1회차 직후 값은 기록하지 않았다. 재색인 시 청크가 늘지 않는 것은 2번에서 확인).</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
-          <t>screenshots/10_history_per_coin_sol.jpg, screenshots/12_live_kimp_answer.jpg</t>
+          <t>ui_history_switch.json, screenshots/10_history_per_coin_sol.jpg, screenshots/12_live_kimp_answer.jpg</t>
         </is>
       </c>
       <c r="I18" s="33" t="inlineStr">
         <is>
-          <t>SOL에서 질문 → BTC로 바꿔 질문 → SOL로 돌아오면 SOL 대화 2건만 남아 있고 BTC 대화가 섞이지 않는다. 코인 전환은 화면의 selectCoin을 직접 호출했다(시세표가 5초마다 다시 그려져 행 클릭 참조가 계속 바뀜).</t>
+          <t>SOL에서 질문 → BTC로 바꿔 질문(캡처 12) → SOL로 돌아오면 SOL의 질문·답변 1쌍만 있고 BTC 대화가 섞이지 않는다(돌아온 직후 대화 목록을 DOM에서 읽은 값: ui_history_switch.json). 새로고침 뒤에도 코인별 기록이 유지된다(캡처 19 하단). 코인 전환은 화면의 selectCoin을 직접 호출했다(시세표가 5초마다 다시 그려져 행 클릭 참조가 계속 바뀜).</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="I20" s="33" t="inlineStr">
         <is>
-          <t>특화 기능(김프 실시간 근거): '지금 비트코인 김프 몇 %야?' → 기준 시각과 +0.86~0.87%를 '실시간 시세 스냅샷' 근거로 인용. 처음 실행에서 '솔라나 김프가 다르게 움직인 이유'에 전제(SOL만 다르다)를 받아들이고 입출금 중지를 원인으로 단정했다. 프롬프트에 전제 확인 규칙을 넣은 뒤 재실행에서는 전제가 근거와 맞지 않는다고 답했다. 입출금 상태 근거는 15분 수집이 아직 돌지 않아 비어 있다(상태 질문은 근거 없음으로 거절).</t>
+          <t>특화 기능(김프 실시간 근거): '지금 비트코인 김프 몇 %야?' → 기준 시각과 +0.86~0.87%를 '실시간 시세 스냅샷' 근거로 인용. 처음 실행에서 '솔라나 김프가 다르게 움직인 이유'에 전제(SOL만 다르다)를 받아들이고 입출금 중지를 원인으로 단정했다. 프롬프트에 전제 확인 규칙을 넣은 뒤 재실행(1회)에서는 전제를 뒷받침하는 근거가 없어 이유를 확인할 수 없다고 답하고 원인을 단정하지 않았다. 입출금 상태 근거는 15분 수집이 아직 돌지 않아 비어 있다(상태 질문은 근거 없음으로 거절).</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="I25" s="33" t="inlineStr">
         <is>
-          <t>질문 5개를 RAG 없이/RAG로 실행(2026-10-22, 실제 모델). RAG 없이 틀림 1(업비트 trade_time을 KST로 답함)·맥락 이탈 1, RAG는 수정 전 문서 속 예시 가격을 현재가로 답한 1건. 질문 세트가 김프 도메인 확정 전이고 판정은 작성 측 수동 대조다.</t>
+          <t>질문 5개를 RAG 없이/RAG로 실행한 기록(evaluation.json, 2026-10-22 PC 실연동 검증 때 생성 — WINDOWS_VERIFICATION.md). 파일에는 날짜·모델 필드가 없다. RAG 없이 틀림 1(업비트 trade_time을 KST로 답함)·맥락 이탈 1, RAG는 수정 전 문서 속 예시 가격을 현재가로 답한 1건. 판정은 Claude가 인용 원문과 대조해 적었고 사람 판정은 없다(원자료 review 칸은 '사람 검토 필요'). 질문 세트는 김프 도메인 확정 전 것이다.</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="H27" s="33" t="inlineStr">
         <is>
-          <t>screenshots/19_citation_source_type.jpg, screenshots/12_live_kimp_answer.jpg, api_run.json</t>
+          <t>screenshots/19_citation_source_type.jpg, screenshots/19_document_panel_after_fix.jpg, api_run.json</t>
         </is>
       </c>
       <c r="I27" s="33" t="inlineStr">
         <is>
-          <t>출처 종류 4가지가 구분 표시된다: 항목 메타데이터, 빗썸 공지 원문(업비트 상태 아님), 실시간 시세 스냅샷, 거래소 API 문서·프로젝트 공식 가이드. 근거 원문 보기에서 거래소·게시·개정 시각도 보인다.</t>
+          <t>답변 근거 목록에는 3종류가 구분 표시된다: 항목 메타데이터, 빗썸 공지 원문(업비트 상태 아님), 실시간 시세 스냅샷. 문서 목록 패널에는 거래소 API 문서·프로젝트 공식 가이드까지 종류와 날짜가 표시된다. 근거 원문 보기에서 거래소·게시·개정 시각도 보인다. 이번 질문들에서는 공식 문서가 선별에서 제외돼 근거 목록에 오르지 않았다.</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I28" s="33" t="inlineStr">
         <is>
-          <t>팀 기준을 '30초 이내 + 처리 중 표시'로 정했다. 첫 질문 23.3초, 같은 질문 재실행 13.8초, 다른 첫 질문 14~26초. 대부분이 생성 모델 호출 시간이다. 투자 판단 질문도 수집을 먼저 해 14초가 걸린다(보류 판정을 앞당기면 줄일 수 있음). 무료 서버가 잠든 뒤 첫 접속은 별도로 30초~1분 더 걸린다.</t>
+          <t>팀 기준을 '30초 이내 + 처리 중 표시'로 정했다. 첫 질문 23.3초, 같은 질문 재실행 13.8초, 다른 첫 질문 14~19초(화면에서 26.1초 1회). 대부분이 생성 모델 호출 시간이다. 투자 판단 질문도 수집을 먼저 해 16.0초가 걸린다(보류 판정을 앞당기면 줄일 수 있음). 무료 서버가 잠든 뒤의 첫 접속 시간은 측정하지 않았다.</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H29" s="33" t="inlineStr">
         <is>
-          <t>api_run.json, .gitignore</t>
+          <t>secret_scan.txt, api_run.json</t>
         </is>
       </c>
       <c r="I29" s="33" t="inlineStr">
         <is>
-          <t>저장소 전체 커밋 이력에서 키 형식 문자열(sk-, npg_, 비밀번호 포함 DB URL) 0건, .env는 .gitignore. 오류 상황(없는 코인 404, Top-k 99 422, 잘못된 기간 400, 잘못된 공지 ID 404)은 짧은 안내만 돌려주고 스택 추적·프롬프트·키가 없다. 422는 입력값 검증 내용(필드·한도)을 보여 준다. 화면 오류는 API 응답으로 확인했다.</t>
+          <t>전체 커밋 이력에서 키 형식 문자열(sk-, npg_, 비밀번호 포함 DB URL, AWS 키, 개인키) 0건, 추적 중인 .env 0개, .env는 .gitignore(secret_scan.txt). 오류 상황(없는 코인 404, Top-k 99 422, 잘못된 기간 400, 잘못된 공지 ID 404)은 짧은 안내만 돌려주고 스택 추적·프롬프트·키가 없다. 422는 입력값 검증 내용(필드·한도)을 보여 준다. 화면 캡처 11장에도 키·오류 상세가 없다. 화면 오류 표시는 API 응답으로 확인했다.</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I31" s="33" t="inlineStr">
         <is>
-          <t>시세 429·502·503 재시도 2회(Retry-After 존중)·5초 캐시, 공식 문서 3회 백오프·요청 간 1초, 빗썸 요청 간 1.1초. 빗썸·공식 문서 요청에 프로젝트 식별 User-Agent. 위키백과는 쓰지 않는다. 빗썸 공지 본문 페이지가 서버 요청을 403으로 막아 관리자 브라우저로 받은 원문을 넘기는 경로를 썼다(우회용 User-Agent 위장은 하지 않음).</t>
+          <t>시세 429·502·503 재시도 2회(Retry-After 존중)·5초 캐시, 공식 문서 3회 백오프·요청 간 1초, 빗썸 공지·상태 요청 간 1.1초. 빗썸 공지·상태와 공식 문서 요청은 프로젝트 식별 User-Agent를 쓴다. 시세 조회(업비트·바이낸스·OKX 등·빗썸 시세 대체)는 브라우저형 User-Agent를 쓴다 — 해당 API 문서에 요구하는 식별 형식이 없어서이며 SOURCES.md에 적었다. 위키백과는 쓰지 않는다. 빗썸 공지 본문 페이지가 서버 요청을 403으로 막아 관리자 브라우저로 받은 원문을 넘기는 경로를 썼다(우회용 User-Agent 위장은 하지 않음).</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="I34" s="33" t="inlineStr">
         <is>
-          <t>증빙 칸의 캡처 10장을 screenshots/에 넣었다. 캡처에 키·오류 상세는 없다. 나머지 증빙은 실행 결과 JSON(api_run.json, local_index.json)이다.</t>
+          <t>증빙 칸의 캡처 11장을 screenshots/에 넣었다. 캡처에 키·오류 상세는 없다. 08·09·13번 캡처의 문서 패널에 보이는 '검색 서버 연결 후 문서를 확인할 수 있습니다.'는 점검 중 발견한 화면 오류이며, 수정 후 캡처는 19_document_panel_after_fix.jpg다.</t>
         </is>
       </c>
     </row>

--- a/docs/checklist/2회차_셀프·상호_체크리스트_셀프점검.xlsx
+++ b/docs/checklist/2회차_셀프·상호_체크리스트_셀프점검.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="체크리스트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 안내" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="체크리스트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="작성 안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'체크리스트'!$8:$8</definedName>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H35" s="33" t="inlineStr">
         <is>
-          <t>README.md, docs/TEST_RESULTS.md, RESULTS.md</t>
+          <t>docs/REQUIREMENTS.md, docs/RAG_DESIGN.md, README.md, docs/TEST_RESULTS.md, RESULTS.md</t>
         </is>
       </c>
       <c r="I35" s="33" t="inlineStr">
         <is>
-          <t>포함: 소스코드, README, 테스트 결과표(docs/TEST_RESULTS.md), 셀프 체크리스트·요구사항별 대조(이 문서), RAG 전후 비교. 빠짐: 요구사항 정의서, RAG 파이프라인 설계문서(별도 문서). 설계 내용은 README 3절에만 있다. 조치: 두 문서 작성 후 재점검. 상호 체크리스트는 상호 점검 시간에 작성.</t>
+          <t>포함: 요구사항 정의서(docs/REQUIREMENTS.md, 요구사항별 구현·확인 대조 포함), RAG 파이프라인 설계문서(docs/RAG_DESIGN.md), 소스코드, README, 테스트 결과표(docs/TEST_RESULTS.md), 셀프 체크리스트(이 문서), RAG 전후 비교. 빠짐: 상호 체크리스트(상호 점검 시간에 작성). 두 문서는 2026-10-23 추가, 상호 체크리스트를 넣은 뒤 재점검.</t>
         </is>
       </c>
     </row>
